--- a/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
+++ b/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="120">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T17:47:08+00:00</t>
+    <t>2026-09-08T17:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>30</t>
+    <t>36</t>
   </si>
   <si>
     <t>Code</t>
@@ -344,6 +344,36 @@
   </si>
   <si>
     <t>Ich bin extrem ängstlich oder deprimiert</t>
+  </si>
+  <si>
+    <t>Level 1</t>
+  </si>
+  <si>
+    <t>Level 2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Level 3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Level 4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Level 5</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Level 9</t>
   </si>
 </sst>
 </file>
@@ -701,7 +731,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1078,6 +1108,78 @@
       </c>
       <c r="D31" s="2"/>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
+++ b/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:30:22+00:00</t>
+    <t>2026-09-11T10:35:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
+++ b/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:35:27+00:00</t>
+    <t>2026-09-11T13:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
+++ b/CodeSystem-mii-cs-pro-eq-5d-value-set.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:28:57+00:00</t>
+    <t>2026-09-11T16:14:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
